--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -4626,7 +4626,7 @@
         <v>132741015</v>
       </c>
       <c r="B38" t="n">
-        <v>58136</v>
+        <v>58167</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4651,12 +4651,19 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bomålefällan, Bomålefällan, Sm</t>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -4626,7 +4626,7 @@
         <v>132741015</v>
       </c>
       <c r="B38" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ39"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2032,32 +2032,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128918881</v>
+        <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>91930</v>
+        <v>92513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2067,19 +2067,21 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578908</v>
+        <v>578828</v>
       </c>
       <c r="R14" t="n">
-        <v>6341535</v>
+        <v>6341589</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,12 +2108,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,71 +2127,81 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128918881</t>
+          <t>https://artportalen.se/Sighting/137069720</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128919463</v>
+        <v>137056134</v>
       </c>
       <c r="B15" t="n">
-        <v>91930</v>
+        <v>92528</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578907</v>
+        <v>578756</v>
       </c>
       <c r="R15" t="n">
-        <v>6341582</v>
+        <v>6341596</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2208,22 +2225,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,27 +2245,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128919463</t>
+          <t>https://artportalen.se/Sighting/137056134</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128920910</v>
+        <v>128918881</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>91930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,37 +2273,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578786</v>
+        <v>578908</v>
       </c>
       <c r="R16" t="n">
-        <v>6341549</v>
+        <v>6341535</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2340,27 +2356,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920910</t>
+          <t>https://artportalen.se/Sighting/128918881</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128920948</v>
+        <v>128919463</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2368,34 +2384,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578790</v>
+        <v>578907</v>
       </c>
       <c r="R17" t="n">
-        <v>6341547</v>
+        <v>6341582</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2425,9 +2441,19 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2442,27 +2468,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920948</t>
+          <t>https://artportalen.se/Sighting/128919463</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128919341</v>
+        <v>137055956</v>
       </c>
       <c r="B18" t="n">
-        <v>79946</v>
+        <v>92138</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2470,37 +2496,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578908</v>
+        <v>578768</v>
       </c>
       <c r="R18" t="n">
-        <v>6341535</v>
+        <v>6341585</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2524,12 +2559,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2555,16 +2590,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128919341</t>
+          <t>https://artportalen.se/Sighting/137055956</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128919819</v>
+        <v>137056000</v>
       </c>
       <c r="B19" t="n">
-        <v>79946</v>
+        <v>92138</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2572,37 +2607,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Fliseryds-Boda 2.3, Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578903</v>
+        <v>578761</v>
       </c>
       <c r="R19" t="n">
-        <v>6341617</v>
+        <v>6341582</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2626,12 +2670,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,16 +2701,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128919819</t>
+          <t>https://artportalen.se/Sighting/137056000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128919941</v>
+        <v>128920910</v>
       </c>
       <c r="B20" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,34 +2718,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578917</v>
+        <v>578786</v>
       </c>
       <c r="R20" t="n">
-        <v>6341627</v>
+        <v>6341549</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2759,16 +2803,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128919941</t>
+          <t>https://artportalen.se/Sighting/128920910</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128920768</v>
+        <v>128920948</v>
       </c>
       <c r="B21" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,37 +2820,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578827</v>
+        <v>578790</v>
       </c>
       <c r="R21" t="n">
-        <v>6341593</v>
+        <v>6341547</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2850,24 +2894,24 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920768</t>
+          <t>https://artportalen.se/Sighting/128920948</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128920836</v>
+        <v>128919341</v>
       </c>
       <c r="B22" t="n">
         <v>79946</v>
@@ -2898,17 +2942,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578760</v>
+        <v>578908</v>
       </c>
       <c r="R22" t="n">
-        <v>6341596</v>
+        <v>6341535</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2963,13 +3007,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920836</t>
+          <t>https://artportalen.se/Sighting/128919341</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128920843</v>
+        <v>128919819</v>
       </c>
       <c r="B23" t="n">
         <v>79946</v>
@@ -3000,17 +3044,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578791</v>
+        <v>578903</v>
       </c>
       <c r="R23" t="n">
-        <v>6341539</v>
+        <v>6341617</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3054,24 +3098,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920843</t>
+          <t>https://artportalen.se/Sighting/128919819</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128920885</v>
+        <v>128919941</v>
       </c>
       <c r="B24" t="n">
         <v>79946</v>
@@ -3102,17 +3146,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578712</v>
+        <v>578917</v>
       </c>
       <c r="R24" t="n">
-        <v>6341655</v>
+        <v>6341627</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3156,24 +3200,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920885</t>
+          <t>https://artportalen.se/Sighting/128919941</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927674</v>
+        <v>128920768</v>
       </c>
       <c r="B25" t="n">
         <v>79946</v>
@@ -3202,22 +3246,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578789</v>
+        <v>578827</v>
       </c>
       <c r="R25" t="n">
-        <v>6341540</v>
+        <v>6341593</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3244,52 +3285,41 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128927674</t>
+          <t>https://artportalen.se/Sighting/128920768</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927695</v>
+        <v>128920836</v>
       </c>
       <c r="B26" t="n">
         <v>79946</v>
@@ -3318,22 +3348,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578814</v>
+        <v>578760</v>
       </c>
       <c r="R26" t="n">
-        <v>6341561</v>
+        <v>6341596</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3360,52 +3387,41 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128927695</t>
+          <t>https://artportalen.se/Sighting/128920836</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128987483</v>
+        <v>128920843</v>
       </c>
       <c r="B27" t="n">
         <v>79946</v>
@@ -3434,26 +3450,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578815</v>
+        <v>578791</v>
       </c>
       <c r="R27" t="n">
-        <v>6341557</v>
+        <v>6341539</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3491,31 +3500,30 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128987483</t>
+          <t>https://artportalen.se/Sighting/128920843</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128987493</v>
+        <v>128920885</v>
       </c>
       <c r="B28" t="n">
         <v>79946</v>
@@ -3544,26 +3552,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578787</v>
+        <v>578712</v>
       </c>
       <c r="R28" t="n">
-        <v>6341556</v>
+        <v>6341655</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3601,7 +3602,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3619,59 +3619,57 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128987493</t>
+          <t>https://artportalen.se/Sighting/128920885</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128919687</v>
+        <v>128927674</v>
       </c>
       <c r="B29" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578913</v>
+        <v>578789</v>
       </c>
       <c r="R29" t="n">
-        <v>6341635</v>
+        <v>6341540</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3698,87 +3696,96 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128919687</t>
+          <t>https://artportalen.se/Sighting/128927674</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128919953</v>
+        <v>128927695</v>
       </c>
       <c r="B30" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578910</v>
+        <v>578814</v>
       </c>
       <c r="R30" t="n">
-        <v>6341608</v>
+        <v>6341561</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3805,87 +3812,100 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128919953</t>
+          <t>https://artportalen.se/Sighting/128927695</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128920205</v>
+        <v>128987483</v>
       </c>
       <c r="B31" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578827</v>
+        <v>578815</v>
       </c>
       <c r="R31" t="n">
-        <v>6341593</v>
+        <v>6341557</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3923,6 +3943,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3940,59 +3961,61 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920205</t>
+          <t>https://artportalen.se/Sighting/128987483</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128920859</v>
+        <v>128987493</v>
       </c>
       <c r="B32" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578715</v>
+        <v>578787</v>
       </c>
       <c r="R32" t="n">
-        <v>6341638</v>
+        <v>6341556</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4030,6 +4053,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4047,13 +4071,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920859</t>
+          <t>https://artportalen.se/Sighting/128987493</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128927562</v>
+        <v>128919687</v>
       </c>
       <c r="B33" t="n">
         <v>57950</v>
@@ -4081,32 +4105,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578536</v>
+        <v>578913</v>
       </c>
       <c r="R33" t="n">
-        <v>6341648</v>
+        <v>6341635</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4133,19 +4150,9 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>17:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4160,24 +4167,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128927562</t>
+          <t>https://artportalen.se/Sighting/128919687</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128987545</v>
+        <v>128919953</v>
       </c>
       <c r="B34" t="n">
         <v>57950</v>
@@ -4206,27 +4213,24 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578607</v>
+        <v>578910</v>
       </c>
       <c r="R34" t="n">
-        <v>6341602</v>
+        <v>6341608</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4281,13 +4285,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128987545</t>
+          <t>https://artportalen.se/Sighting/128919953</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128987559</v>
+        <v>128920205</v>
       </c>
       <c r="B35" t="n">
         <v>57950</v>
@@ -4316,27 +4320,24 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578577</v>
+        <v>578827</v>
       </c>
       <c r="R35" t="n">
-        <v>6341635</v>
+        <v>6341593</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4391,16 +4392,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128987559</t>
+          <t>https://artportalen.se/Sighting/128920205</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128920974</v>
+        <v>128920859</v>
       </c>
       <c r="B36" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4408,16 +4409,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4426,19 +4427,24 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578791</v>
+        <v>578715</v>
       </c>
       <c r="R36" t="n">
-        <v>6341539</v>
+        <v>6341638</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4482,27 +4488,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920974</t>
+          <t>https://artportalen.se/Sighting/128920859</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128927635</v>
+        <v>128927562</v>
       </c>
       <c r="B37" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4510,16 +4516,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4529,7 +4535,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -4546,10 +4552,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578684</v>
+        <v>578536</v>
       </c>
       <c r="R37" t="n">
-        <v>6341612</v>
+        <v>6341648</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4617,66 +4623,62 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128927635</t>
+          <t>https://artportalen.se/Sighting/128927562</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132741015</v>
+        <v>128987545</v>
       </c>
       <c r="B38" t="n">
-        <v>58169</v>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578930</v>
+        <v>578607</v>
       </c>
       <c r="R38" t="n">
-        <v>6341549</v>
+        <v>6341602</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4700,22 +4702,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4730,27 +4722,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132741015</t>
+          <t>https://artportalen.se/Sighting/128987545</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132740648</v>
+        <v>128987559</v>
       </c>
       <c r="B39" t="n">
-        <v>5201</v>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4758,16 +4750,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4776,16 +4768,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578886</v>
+        <v>578577</v>
       </c>
       <c r="R39" t="n">
-        <v>6341561</v>
+        <v>6341635</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4812,22 +4812,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4842,16 +4832,801 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128987559</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137069695</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stenbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>578892</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6341593</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137069695</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128920974</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bomålefällan, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>578791</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6341539</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Cecilia  Ribbing</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Cecilia  Ribbing</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920974</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128927635</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stenbäcken, Boda, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>578684</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6341612</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128927635</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132741015</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>578930</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6341549</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132741015</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137056067</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Fliseryds-Boda 2.3, Fliseryds-Boda 2.3, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>578762</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6341578</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137056067</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137056513</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Fliseryds-Boda 2.3, Fliseryds-Boda 2.3, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>578673</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6341601</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137056513</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132740648</v>
+      </c>
+      <c r="B46" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>578886</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6341561</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132740648</t>
         </is>
@@ -4897,6 +5672,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ46"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2151,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137056134</v>
+        <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92528</v>
+        <v>92513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,43 +2162,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>4217</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Gökhult Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578756</v>
+        <v>578834</v>
       </c>
       <c r="R15" t="n">
-        <v>6341596</v>
+        <v>6341593</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,9 +2219,19 @@
           <t>2026-10-04</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2245,74 +2246,74 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137056134</t>
+          <t>https://artportalen.se/Sighting/137073601</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128918881</v>
+        <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>91930</v>
+        <v>92528</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578908</v>
+        <v>578756</v>
       </c>
       <c r="R16" t="n">
-        <v>6341535</v>
+        <v>6341596</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2336,12 +2337,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,54 +2368,54 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128918881</t>
+          <t>https://artportalen.se/Sighting/137056134</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128919463</v>
+        <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>91930</v>
+        <v>92528</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Gökhult Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578907</v>
+        <v>578751</v>
       </c>
       <c r="R17" t="n">
-        <v>6341582</v>
+        <v>6341592</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2438,22 +2439,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,27 +2469,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128919463</t>
+          <t>https://artportalen.se/Sighting/137073607</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137055956</v>
+        <v>128918881</v>
       </c>
       <c r="B18" t="n">
-        <v>92138</v>
+        <v>91930</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2515,27 +2516,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578768</v>
+        <v>578908</v>
       </c>
       <c r="R18" t="n">
-        <v>6341585</v>
+        <v>6341535</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2559,12 +2560,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2590,16 +2591,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137055956</t>
+          <t>https://artportalen.se/Sighting/128918881</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137056000</v>
+        <v>128919463</v>
       </c>
       <c r="B19" t="n">
-        <v>92138</v>
+        <v>91930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,29 +2625,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Fliseryds-Boda 2.3, Sm</t>
+          <t>Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578761</v>
+        <v>578907</v>
       </c>
       <c r="R19" t="n">
         <v>6341582</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2670,12 +2662,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2690,27 +2692,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137056000</t>
+          <t>https://artportalen.se/Sighting/128919463</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128920910</v>
+        <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>92138</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,37 +2720,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578786</v>
+        <v>578768</v>
       </c>
       <c r="R20" t="n">
-        <v>6341549</v>
+        <v>6341585</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2772,12 +2783,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2792,27 +2803,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920910</t>
+          <t>https://artportalen.se/Sighting/137055956</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128920948</v>
+        <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>92138</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,37 +2831,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Fliseryds-Boda 2.3, Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578790</v>
+        <v>578761</v>
       </c>
       <c r="R21" t="n">
-        <v>6341547</v>
+        <v>6341582</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2874,12 +2894,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2894,27 +2914,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920948</t>
+          <t>https://artportalen.se/Sighting/137056000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128919341</v>
+        <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>79946</v>
+        <v>92138</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,34 +2942,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Gökhult Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578908</v>
+        <v>578911</v>
       </c>
       <c r="R22" t="n">
-        <v>6341535</v>
+        <v>6341534</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2976,12 +2996,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2996,27 +3026,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128919341</t>
+          <t>https://artportalen.se/Sighting/137073589</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128919819</v>
+        <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>79946</v>
+        <v>93453</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3024,37 +3054,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Gökhult Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578903</v>
+        <v>578749</v>
       </c>
       <c r="R23" t="n">
-        <v>6341617</v>
+        <v>6341594</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3078,12 +3108,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3098,27 +3138,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128919819</t>
+          <t>https://artportalen.se/Sighting/137073608</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128919941</v>
+        <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>79946</v>
+        <v>93453</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3126,37 +3166,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Gökhult Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578917</v>
+        <v>578723</v>
       </c>
       <c r="R24" t="n">
-        <v>6341627</v>
+        <v>6341619</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3180,12 +3220,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3200,27 +3250,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128919941</t>
+          <t>https://artportalen.se/Sighting/137073609</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128920768</v>
+        <v>128920910</v>
       </c>
       <c r="B25" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3228,21 +3278,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3252,13 +3302,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578827</v>
+        <v>578786</v>
       </c>
       <c r="R25" t="n">
-        <v>6341593</v>
+        <v>6341549</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3302,27 +3352,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920768</t>
+          <t>https://artportalen.se/Sighting/128920910</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128920836</v>
+        <v>128920948</v>
       </c>
       <c r="B26" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3330,37 +3380,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578760</v>
+        <v>578790</v>
       </c>
       <c r="R26" t="n">
-        <v>6341596</v>
+        <v>6341547</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3404,24 +3454,24 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920836</t>
+          <t>https://artportalen.se/Sighting/128920948</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128920843</v>
+        <v>128919341</v>
       </c>
       <c r="B27" t="n">
         <v>79946</v>
@@ -3456,13 +3506,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578791</v>
+        <v>578908</v>
       </c>
       <c r="R27" t="n">
-        <v>6341539</v>
+        <v>6341535</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3506,24 +3556,24 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920843</t>
+          <t>https://artportalen.se/Sighting/128919341</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128920885</v>
+        <v>128919819</v>
       </c>
       <c r="B28" t="n">
         <v>79946</v>
@@ -3558,13 +3608,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578712</v>
+        <v>578903</v>
       </c>
       <c r="R28" t="n">
-        <v>6341655</v>
+        <v>6341617</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3619,13 +3669,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920885</t>
+          <t>https://artportalen.se/Sighting/128919819</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128927674</v>
+        <v>128919941</v>
       </c>
       <c r="B29" t="n">
         <v>79946</v>
@@ -3654,22 +3704,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578789</v>
+        <v>578917</v>
       </c>
       <c r="R29" t="n">
-        <v>6341540</v>
+        <v>6341627</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3696,52 +3743,41 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128927674</t>
+          <t>https://artportalen.se/Sighting/128919941</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128927695</v>
+        <v>128920768</v>
       </c>
       <c r="B30" t="n">
         <v>79946</v>
@@ -3770,22 +3806,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578814</v>
+        <v>578827</v>
       </c>
       <c r="R30" t="n">
-        <v>6341561</v>
+        <v>6341593</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3812,52 +3845,41 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128927695</t>
+          <t>https://artportalen.se/Sighting/128920768</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128987483</v>
+        <v>128920836</v>
       </c>
       <c r="B31" t="n">
         <v>79946</v>
@@ -3886,23 +3908,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578815</v>
+        <v>578760</v>
       </c>
       <c r="R31" t="n">
-        <v>6341557</v>
+        <v>6341596</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3943,7 +3958,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3961,13 +3975,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128987483</t>
+          <t>https://artportalen.se/Sighting/128920836</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128987493</v>
+        <v>128920843</v>
       </c>
       <c r="B32" t="n">
         <v>79946</v>
@@ -3996,26 +4010,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Sm</t>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578787</v>
+        <v>578791</v>
       </c>
       <c r="R32" t="n">
-        <v>6341556</v>
+        <v>6341539</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4053,77 +4060,71 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Cecilia  Ribbing</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128987493</t>
+          <t>https://artportalen.se/Sighting/128920843</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128919687</v>
+        <v>128920885</v>
       </c>
       <c r="B33" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578913</v>
+        <v>578712</v>
       </c>
       <c r="R33" t="n">
-        <v>6341635</v>
+        <v>6341655</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4178,59 +4179,57 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128919687</t>
+          <t>https://artportalen.se/Sighting/128920885</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128919953</v>
+        <v>128927674</v>
       </c>
       <c r="B34" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578910</v>
+        <v>578789</v>
       </c>
       <c r="R34" t="n">
-        <v>6341608</v>
+        <v>6341540</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4257,87 +4256,96 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128919953</t>
+          <t>https://artportalen.se/Sighting/128927674</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128920205</v>
+        <v>128927695</v>
       </c>
       <c r="B35" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Stenbäcken, Boda, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578827</v>
+        <v>578814</v>
       </c>
       <c r="R35" t="n">
-        <v>6341593</v>
+        <v>6341561</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4364,87 +4372,100 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920205</t>
+          <t>https://artportalen.se/Sighting/128927695</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128920859</v>
+        <v>128987483</v>
       </c>
       <c r="B36" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pyttehagen, Pyttehagen, Sm</t>
+          <t>Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578715</v>
+        <v>578815</v>
       </c>
       <c r="R36" t="n">
-        <v>6341638</v>
+        <v>6341557</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4482,6 +4503,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4499,66 +4521,61 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920859</t>
+          <t>https://artportalen.se/Sighting/128987483</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128927562</v>
+        <v>128987493</v>
       </c>
       <c r="B37" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stenbäcken, Boda, Sm</t>
+          <t>Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578536</v>
+        <v>578787</v>
       </c>
       <c r="R37" t="n">
-        <v>6341648</v>
+        <v>6341556</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4585,51 +4602,42 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128927562</t>
+          <t>https://artportalen.se/Sighting/128987493</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128987545</v>
+        <v>128919687</v>
       </c>
       <c r="B38" t="n">
         <v>57950</v>
@@ -4658,24 +4666,21 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578607</v>
+        <v>578913</v>
       </c>
       <c r="R38" t="n">
-        <v>6341602</v>
+        <v>6341635</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4733,13 +4738,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128987545</t>
+          <t>https://artportalen.se/Sighting/128919687</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128987559</v>
+        <v>128919953</v>
       </c>
       <c r="B39" t="n">
         <v>57950</v>
@@ -4768,27 +4773,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578577</v>
+        <v>578910</v>
       </c>
       <c r="R39" t="n">
-        <v>6341635</v>
+        <v>6341608</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4843,16 +4845,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128987559</t>
+          <t>https://artportalen.se/Sighting/128919953</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137069695</v>
+        <v>128920205</v>
       </c>
       <c r="B40" t="n">
-        <v>57195</v>
+        <v>57950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4860,45 +4862,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stenbäcken, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578892</v>
+        <v>578827</v>
       </c>
       <c r="R40" t="n">
         <v>6341593</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4922,12 +4921,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4942,27 +4941,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137069695</t>
+          <t>https://artportalen.se/Sighting/128920205</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128920974</v>
+        <v>128920859</v>
       </c>
       <c r="B41" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4970,16 +4969,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4988,19 +4987,24 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bomålefällan, Sm</t>
+          <t>Pyttehagen, Pyttehagen, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578791</v>
+        <v>578715</v>
       </c>
       <c r="R41" t="n">
-        <v>6341539</v>
+        <v>6341638</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5044,27 +5048,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia  Ribbing</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128920974</t>
+          <t>https://artportalen.se/Sighting/128920859</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128927635</v>
+        <v>128927562</v>
       </c>
       <c r="B42" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5072,16 +5076,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5091,7 +5095,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -5108,10 +5112,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578684</v>
+        <v>578536</v>
       </c>
       <c r="R42" t="n">
-        <v>6341612</v>
+        <v>6341648</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5179,66 +5183,62 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128927635</t>
+          <t>https://artportalen.se/Sighting/128927562</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132741015</v>
+        <v>128987545</v>
       </c>
       <c r="B43" t="n">
-        <v>58169</v>
+        <v>57950</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578930</v>
+        <v>578607</v>
       </c>
       <c r="R43" t="n">
-        <v>6341549</v>
+        <v>6341602</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5262,22 +5262,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5292,71 +5282,70 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132741015</t>
+          <t>https://artportalen.se/Sighting/128987545</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137056067</v>
+        <v>128987559</v>
       </c>
       <c r="B44" t="n">
-        <v>58169</v>
+        <v>57950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Fliseryds-Boda 2.3, Sm</t>
+          <t>Fliseryds-Boda 2.3, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578762</v>
+        <v>578577</v>
       </c>
       <c r="R44" t="n">
-        <v>6341578</v>
+        <v>6341635</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5383,12 +5372,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5414,16 +5403,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137056067</t>
+          <t>https://artportalen.se/Sighting/128987559</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137056513</v>
+        <v>137069695</v>
       </c>
       <c r="B45" t="n">
-        <v>58164</v>
+        <v>57195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5431,34 +5420,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103023</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fliseryds-Boda 2.3, Fliseryds-Boda 2.3, Sm</t>
+          <t>Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578673</v>
+        <v>578892</v>
       </c>
       <c r="R45" t="n">
-        <v>6341601</v>
+        <v>6341593</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5505,27 +5502,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137056513</t>
+          <t>https://artportalen.se/Sighting/137069695</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132740648</v>
+        <v>137073596</v>
       </c>
       <c r="B46" t="n">
-        <v>5201</v>
+        <v>57195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5533,37 +5530,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bomålefällan, Bomålefällan, Sm</t>
+          <t>Gökhult Stenbäcken, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578886</v>
+        <v>578894</v>
       </c>
       <c r="R46" t="n">
-        <v>6341561</v>
+        <v>6341580</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5587,22 +5588,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Skitar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5617,18 +5623,1381 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137073596</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128920974</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Bomålefällan, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>578791</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6341539</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Cecilia  Ribbing</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Cecilia  Ribbing</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920974</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128927635</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stenbäcken, Boda, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>578684</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6341612</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128927635</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>137073606</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58283</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103019</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Stjärtmes</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Aegithalos caudatus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gökhult Stenbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>578762</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6341585</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073606</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132741015</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>578930</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6341549</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132741015</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137056067</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Fliseryds-Boda 2.3, Fliseryds-Boda 2.3, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>578762</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6341578</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137056067</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>137073590</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Gökhult Stenbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>578924</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6341576</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073590</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137073598</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gökhult Stenbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>578893</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6341584</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073598</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137073604</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gökhult Stenbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>578745</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6341602</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073604</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>137056513</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Fliseryds-Boda 2.3, Fliseryds-Boda 2.3, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>578673</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6341601</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137056513</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>137073605</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Gökhult Stenbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>578747</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6341570</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073605</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132740648</v>
+      </c>
+      <c r="B57" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Bomålefällan, Bomålefällan, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>578886</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6341561</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/132740648</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>137073600</v>
+      </c>
+      <c r="B58" t="n">
+        <v>58872</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Gökhult Stenbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>578827</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6341574</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073600</t>
         </is>
       </c>
     </row>
@@ -5679,6 +7048,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>92513</v>
+        <v>92514</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92513</v>
+        <v>92514</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>92528</v>
+        <v>92529</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>92528</v>
+        <v>92529</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>92514</v>
+        <v>92520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92514</v>
+        <v>92520</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>92529</v>
+        <v>92535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>92529</v>
+        <v>92535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>92535</v>
+        <v>92539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>92535</v>
+        <v>92539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>92526</v>
+        <v>92539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92526</v>
+        <v>92539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>92541</v>
+        <v>92554</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>92541</v>
+        <v>92554</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>137069695</v>
       </c>
       <c r="B45" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>137073596</v>
       </c>
       <c r="B46" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>137073606</v>
       </c>
       <c r="B49" t="n">
-        <v>58283</v>
+        <v>58296</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>132741015</v>
       </c>
       <c r="B50" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>137056067</v>
       </c>
       <c r="B51" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>137073590</v>
       </c>
       <c r="B52" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>137073598</v>
       </c>
       <c r="B53" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>137073604</v>
       </c>
       <c r="B54" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>137056513</v>
       </c>
       <c r="B55" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>137073605</v>
       </c>
       <c r="B56" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>137073600</v>
       </c>
       <c r="B58" t="n">
-        <v>58872</v>
+        <v>58885</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>137069695</v>
       </c>
       <c r="B45" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>137073596</v>
       </c>
       <c r="B46" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>137073606</v>
       </c>
       <c r="B49" t="n">
-        <v>58296</v>
+        <v>58298</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>132741015</v>
       </c>
       <c r="B50" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>137056067</v>
       </c>
       <c r="B51" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>137073590</v>
       </c>
       <c r="B52" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>137073598</v>
       </c>
       <c r="B53" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>137073604</v>
       </c>
       <c r="B54" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>137056513</v>
       </c>
       <c r="B55" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>137073605</v>
       </c>
       <c r="B56" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>137073600</v>
       </c>
       <c r="B58" t="n">
-        <v>58885</v>
+        <v>58887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -5440,11 +5440,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6135,11 +6131,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fliseryds-Boda 2.3, Fliseryds-Boda 2.3, Sm</t>
@@ -6356,11 +6348,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6476,11 +6464,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>92541</v>
+        <v>92544</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92541</v>
+        <v>92544</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>92556</v>
+        <v>92559</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>92556</v>
+        <v>92559</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>92544</v>
+        <v>92554</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92544</v>
+        <v>92554</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>92559</v>
+        <v>92569</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>92559</v>
+        <v>92569</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>137069695</v>
       </c>
       <c r="B45" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>137073596</v>
       </c>
       <c r="B46" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>137073606</v>
       </c>
       <c r="B49" t="n">
-        <v>58298</v>
+        <v>58308</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>137056067</v>
       </c>
       <c r="B51" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>137073590</v>
       </c>
       <c r="B52" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>137073598</v>
       </c>
       <c r="B53" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>137073604</v>
       </c>
       <c r="B54" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>137056513</v>
       </c>
       <c r="B55" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>137073605</v>
       </c>
       <c r="B56" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>137073600</v>
       </c>
       <c r="B58" t="n">
-        <v>58887</v>
+        <v>58897</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>92554</v>
+        <v>92555</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92554</v>
+        <v>92555</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>92569</v>
+        <v>92570</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>92569</v>
+        <v>92570</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>92555</v>
+        <v>92558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92555</v>
+        <v>92558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>92570</v>
+        <v>92573</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>92570</v>
+        <v>92573</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>137069695</v>
       </c>
       <c r="B45" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>137073596</v>
       </c>
       <c r="B46" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>137073606</v>
       </c>
       <c r="B49" t="n">
-        <v>58308</v>
+        <v>58309</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>137056067</v>
       </c>
       <c r="B51" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>137073590</v>
       </c>
       <c r="B52" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>137073598</v>
       </c>
       <c r="B53" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>137073604</v>
       </c>
       <c r="B54" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>137056513</v>
       </c>
       <c r="B55" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>137073605</v>
       </c>
       <c r="B56" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>137073600</v>
       </c>
       <c r="B58" t="n">
-        <v>58897</v>
+        <v>58899</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gabriel Johansson</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2154,7 +2154,7 @@
         <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>92573</v>
+        <v>92575</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>92573</v>
+        <v>92575</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>92560</v>
+        <v>92565</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand, Gabriel Johansson</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2154,7 +2154,7 @@
         <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92560</v>
+        <v>92565</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>92575</v>
+        <v>92580</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>92575</v>
+        <v>92580</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5865,7 +5865,7 @@
         <v>137073606</v>
       </c>
       <c r="B49" t="n">
-        <v>58309</v>
+        <v>58310</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>137056067</v>
       </c>
       <c r="B51" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>137073590</v>
       </c>
       <c r="B52" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>137073598</v>
       </c>
       <c r="B53" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>137073604</v>
       </c>
       <c r="B54" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>137056513</v>
       </c>
       <c r="B55" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>137073605</v>
       </c>
       <c r="B56" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>137073600</v>
       </c>
       <c r="B58" t="n">
-        <v>58899</v>
+        <v>58903</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>92565</v>
+        <v>92577</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92565</v>
+        <v>92577</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>92580</v>
+        <v>92592</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>92580</v>
+        <v>92592</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>92577</v>
+        <v>92578</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92577</v>
+        <v>92578</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>92592</v>
+        <v>92593</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>92592</v>
+        <v>92593</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>92578</v>
+        <v>92581</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92578</v>
+        <v>92581</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>92593</v>
+        <v>92596</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>92593</v>
+        <v>92596</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42153-2025 artfynd.xlsx
+++ b/artfynd/A 42153-2025 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>137069720</v>
       </c>
       <c r="B14" t="n">
-        <v>92581</v>
+        <v>92585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137073601</v>
       </c>
       <c r="B15" t="n">
-        <v>92581</v>
+        <v>92585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137056134</v>
       </c>
       <c r="B16" t="n">
-        <v>92596</v>
+        <v>92600</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>137073607</v>
       </c>
       <c r="B17" t="n">
-        <v>92596</v>
+        <v>92600</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137055956</v>
       </c>
       <c r="B20" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>137056000</v>
       </c>
       <c r="B21" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137073589</v>
       </c>
       <c r="B22" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137073608</v>
       </c>
       <c r="B23" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137073609</v>
       </c>
       <c r="B24" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>137069695</v>
       </c>
       <c r="B45" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>137073596</v>
       </c>
       <c r="B46" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>137073606</v>
       </c>
       <c r="B49" t="n">
-        <v>58310</v>
+        <v>58313</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>137056067</v>
       </c>
       <c r="B51" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>137073590</v>
       </c>
       <c r="B52" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>137073598</v>
       </c>
       <c r="B53" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>137073604</v>
       </c>
       <c r="B54" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>137056513</v>
       </c>
       <c r="B55" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>137073605</v>
       </c>
       <c r="B56" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>137073600</v>
       </c>
       <c r="B58" t="n">
-        <v>58903</v>
+        <v>58906</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
